--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.88549882426335</v>
+        <v>7.618893558942795</v>
       </c>
       <c r="D2" t="n">
-        <v>47.10569864669393</v>
+        <v>7.654676030087764</v>
       </c>
       <c r="E2" t="n">
-        <v>6.834894982359292</v>
+        <v>1.110670434633385</v>
       </c>
       <c r="F2" t="n">
-        <v>6.926776518684789</v>
+        <v>1.125601184286278</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.20298282816387</v>
+        <v>5.720484709576628</v>
       </c>
       <c r="D3" t="n">
-        <v>34.56733354913054</v>
+        <v>5.617191701733713</v>
       </c>
       <c r="E3" t="n">
-        <v>6.834894982359292</v>
+        <v>1.110670434633385</v>
       </c>
       <c r="F3" t="n">
-        <v>6.926776518684789</v>
+        <v>1.125601184286278</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.07611274613499</v>
+        <v>5.212368321246936</v>
       </c>
       <c r="D4" t="n">
-        <v>32.08326928167474</v>
+        <v>5.213531258272146</v>
       </c>
       <c r="E4" t="n">
-        <v>6.834894982359292</v>
+        <v>1.110670434633385</v>
       </c>
       <c r="F4" t="n">
-        <v>6.926776518684789</v>
+        <v>1.125601184286278</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.87066984901779</v>
+        <v>4.528983850465391</v>
       </c>
       <c r="D5" t="n">
-        <v>27.64738806928834</v>
+        <v>4.492700561259356</v>
       </c>
       <c r="E5" t="n">
-        <v>6.834894982359292</v>
+        <v>1.110670434633385</v>
       </c>
       <c r="F5" t="n">
-        <v>6.926776518684789</v>
+        <v>1.125601184286278</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.99615792238917</v>
+        <v>4.71187566238824</v>
       </c>
       <c r="D6" t="n">
-        <v>29.11690376747801</v>
+        <v>4.731496862215177</v>
       </c>
       <c r="E6" t="n">
-        <v>6.834894982359292</v>
+        <v>1.110670434633385</v>
       </c>
       <c r="F6" t="n">
-        <v>6.926776518684789</v>
+        <v>1.125601184286278</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
